--- a/output/laminas_provinciales/prov_i_peringrmin_a_2022_aysen.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2022_aysen.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -408,7 +408,7 @@
         <v>4.63</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -426,7 +426,7 @@
         <v>2.74</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -444,13 +444,13 @@
         <v>3.57</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Capitán Prat</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -459,16 +459,25 @@
         </is>
       </c>
       <c r="C5">
-        <v>4.03</v>
+        <v>4.67</v>
+      </c>
+      <c r="D5">
+        <v>5.06</v>
+      </c>
+      <c r="E5">
+        <v>-0.3899999999999997</v>
+      </c>
+      <c r="F5">
+        <v>-7.707509881422913</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Capitán Prat</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -477,16 +486,25 @@
         </is>
       </c>
       <c r="C6">
-        <v>4.05</v>
+        <v>3.31</v>
+      </c>
+      <c r="D6">
+        <v>3.42</v>
+      </c>
+      <c r="E6">
+        <v>-0.1099999999999999</v>
+      </c>
+      <c r="F6">
+        <v>-3.216374269005839</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Capitán Prat</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -495,16 +513,25 @@
         </is>
       </c>
       <c r="C7">
-        <v>4.04</v>
+        <v>3.96</v>
+      </c>
+      <c r="D7">
+        <v>4.18</v>
+      </c>
+      <c r="E7">
+        <v>-0.2199999999999998</v>
+      </c>
+      <c r="F7">
+        <v>-5.263157894736836</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Coyhaique</t>
+          <t>Capitán Prat</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -513,16 +540,16 @@
         </is>
       </c>
       <c r="C8">
-        <v>4.66</v>
+        <v>4.03</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Coyhaique</t>
+          <t>Capitán Prat</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -531,16 +558,16 @@
         </is>
       </c>
       <c r="C9">
-        <v>3.48</v>
+        <v>4.05</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Coyhaique</t>
+          <t>Capitán Prat</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -549,16 +576,16 @@
         </is>
       </c>
       <c r="C10">
-        <v>4.07</v>
+        <v>4.04</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>General Carrera</t>
+          <t>Coyhaique</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -567,16 +594,16 @@
         </is>
       </c>
       <c r="C11">
-        <v>5.45</v>
+        <v>4.66</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>General Carrera</t>
+          <t>Coyhaique</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -585,27 +612,81 @@
         </is>
       </c>
       <c r="C12">
-        <v>4.23</v>
+        <v>3.48</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Coyhaique</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>4.07</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>General Carrera</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>5.45</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>General Carrera</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>4.23</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>General Carrera</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C13">
+      <c r="C16">
         <v>4.76</v>
       </c>
-      <c r="G13">
+      <c r="G16">
         <v>1</v>
       </c>
     </row>
@@ -678,7 +759,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -919,6 +1000,60 @@
         <v>0</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>3.96</v>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>2.87</v>
+      </c>
+      <c r="D15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>3.56</v>
+      </c>
+      <c r="D16" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/output/laminas_provinciales/prov_i_peringrmin_a_2022_aysen.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2022_aysen.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t xml:space="preserve">Provincia</t>
   </si>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 22:20</t>
+    <t xml:space="preserve">2026-08-19 13:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -86,13 +86,19 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">prov_i_peringrmin_a_2022_aysen.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">% con ingreso igual al mínimo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Region de Aysén</t>
   </si>
   <si>
     <t xml:space="preserve">Año</t>
@@ -833,23 +839,23 @@
         <v>23</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -872,7 +878,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2">
@@ -929,10 +935,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2">
@@ -940,7 +946,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>3.57</v>
@@ -951,7 +957,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>2.49</v>
@@ -962,7 +968,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>3.11</v>
@@ -973,7 +979,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>4.04</v>
@@ -984,7 +990,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>2.72</v>
@@ -995,7 +1001,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>4.51</v>
@@ -1006,7 +1012,7 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>4.07</v>
@@ -1017,7 +1023,7 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>2.97</v>
@@ -1028,7 +1034,7 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>3.71</v>
@@ -1039,7 +1045,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>4.76</v>
@@ -1050,7 +1056,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>3.96</v>
@@ -1061,7 +1067,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>3.8</v>
@@ -1072,7 +1078,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>3.96</v>
@@ -1083,7 +1089,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>2.87</v>
@@ -1094,7 +1100,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>3.56</v>

--- a/output/laminas_provinciales/prov_i_peringrmin_a_2022_aysen.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2022_aysen.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 13:51</t>
+    <t xml:space="preserve">2026-09-07 11:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
